--- a/assets/data/excel/subRaceTalents.xlsx
+++ b/assets/data/excel/subRaceTalents.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="子种族天赋表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subRaceTalents" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -25,13 +25,35 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="004472C4"/>
+        <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0070AD47"/>
+        <bgColor rgb="0070AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -46,8 +68,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -415,197 +446,211 @@
   </sheetPr>
   <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>talentId</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>race</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>subRace</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>subRaceName</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>subRaceNameEn</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>talentName</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>talentNameEn</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>talentType</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>talentDescription</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>effectType</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>effectValue</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>cooldown</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="3" t="inlineStr">
         <is>
           <t>天赋ID</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>种族</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>子种族ID</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>子种族</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>子种族名称</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>子种族英文名</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>天赋名称</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>天赋英文名</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>天赋类型</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="3" t="inlineStr">
         <is>
           <t>天赋描述</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>效果类型</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>效果值</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>冷却</t>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>效果数值</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>冷却回合</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T_PL01</t>
+          <t>T_plant_01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -630,7 +675,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>孢子传播</t>
+          <t>孢子扩散</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -640,32 +685,30 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>passive</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>释放孢子云，对全体敌人造成攻击力80%伤害并降低命中30%，持续2回合</t>
+          <t>菌丝网络在体内形成共生回路，每回合自动释放修复孢子，恢复自身最大生命值的3%，持续5回合后刷新</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>aoe_damage_debuff</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0.8,0.3,2</t>
-        </is>
+          <t>healPercent</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>0.03</v>
       </c>
       <c r="L4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T_PL02</t>
+          <t>T_plant_02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -690,12 +733,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>花粉治愈</t>
+          <t>毒素花粉</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pollen Heal</t>
+          <t>Toxic Pollen</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -705,27 +748,25 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>释放治愈花粉，恢复全体友军攻击力40%的生命值</t>
+          <t>释放高浓度生物毒素花粉，对敌方全体造成攻击力25%的伤害，并附加持续2回合的中毒状态，每回合损失2%最大生命值</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>heal_aoe</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.4</t>
-        </is>
+          <t>aoeDamage</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>0.25</v>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T_PL03</t>
+          <t>T_plant_03</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -750,12 +791,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>缠绕束缚</t>
+          <t>绞杀藤蔓</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Vine Bind</t>
+          <t>Strangling Vine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -765,18 +806,16 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>用藤蔓缠绕单体敌人，造成100%伤害并禁锢2回合</t>
+          <t>从地面召唤变异藤蔓缠绕单个目标，造成攻击力40%的伤害并禁锢1回合，目标无法行动</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>single_damage_stun</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>1.0,2</t>
-        </is>
+          <t>singleDamage</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>0.4</v>
       </c>
       <c r="L6" t="n">
         <v>3</v>
@@ -785,7 +824,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>T_PL04</t>
+          <t>T_plant_04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -810,12 +849,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>树皮护甲</t>
+          <t>木质硬化</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Bark Armor</t>
+          <t>Bark Hardening</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -825,18 +864,16 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>永久提升自身最大生命值20%和减伤5%</t>
+          <t>体表木质纤维密度提升，防御力永久增加15%，受到致命伤害时有20%概率保留1点生命值</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>hp_boost_defense</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.2,0.05</t>
-        </is>
+          <t>defBoost</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>0.15</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -845,7 +882,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T_PL05</t>
+          <t>T_plant_05</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -870,12 +907,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>针刺反击</t>
+          <t>针刺反射</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Thorn Counter</t>
+          <t>Needle Reflect</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -885,18 +922,16 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>受到攻击时，反弹受到伤害的15%给攻击者</t>
+          <t>体表覆盖纳米级变异针刺，受到近战攻击时反弹10%的伤害给攻击者，持续整场战斗</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>damage_reflect</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
+          <t>reflectDamage</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>0.1</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -905,7 +940,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>T_PL06</t>
+          <t>T_plant_06</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -930,12 +965,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>水下呼吸</t>
+          <t>水生适应</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Underwater Breathing</t>
+          <t>Aquatic Adaptation</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -945,18 +980,16 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>每回合恢复自身5%最大生命值，免疫溺水效果</t>
+          <t>水草基因赋予水下作战优势，在水域环境中所有属性提升12%，免疫溺水与水压伤害</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>regen_immune</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.05</t>
-        </is>
+          <t>envBoost</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>0.12</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -965,7 +998,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T_AN01</t>
+          <t>T_animal_01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1005,27 +1038,25 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>从暗处突袭单体敌人，造成180%伤害并附加流血</t>
+          <t>利用猫科动物的超强敏捷进行瞬移突袭，对单个目标造成攻击力55%的伤害，暴击率提升30%</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>single_damage_bleed</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>1.8</t>
-        </is>
+          <t>singleDamage</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>0.55</v>
       </c>
       <c r="L10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T_AN02</t>
+          <t>T_animal_02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1065,27 +1096,25 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>发出战嚎，提升全体友军攻击力15%和暴击率10%，持续2回合</t>
+          <t>发出高频战嚎声波，提升己方全体攻击力12%和速度8%，持续3回合</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>team_buff</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.15,0.1,2</t>
-        </is>
+          <t>teamBuff</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>0.12</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T_AN03</t>
+          <t>T_animal_03</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1115,7 +1144,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Aerial Dive</t>
+          <t>Dive Bomb</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1125,27 +1154,25 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>从高空俯冲攻击，对单体造成200%伤害，无视30%防御</t>
+          <t>飞至高空后高速俯冲，对单个目标造成攻击力60%的伤害，无视目标20%防御</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>single_damage_penetrate</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2.0,0.3</t>
-        </is>
+          <t>singleDamage</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>0.6</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>T_AN04</t>
+          <t>T_animal_04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1155,7 +1182,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>aquatic</t>
+          <t>fish</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1165,47 +1192,45 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aquatic</t>
+          <t>Fish</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>水流冲击</t>
+          <t>鳞甲护盾</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Water Surge</t>
+          <t>Scale Shield</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>passive</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>掀起水流冲击全体敌人，造成90%伤害并降低速度20%</t>
+          <t>变异鳞甲形成生物能量护盾，每回合开始时获得相当于最大生命值8%的临时护盾</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>aoe_damage_slow</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.9,0.2</t>
-        </is>
+          <t>shieldPercent</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>0.08</v>
       </c>
       <c r="L13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>T_AN05</t>
+          <t>T_animal_05</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1230,42 +1255,40 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>蜕皮再生</t>
+          <t>再生蜕皮</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Molt Regeneration</t>
+          <t>Regenerative Molt</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>passive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>受到致命伤害时，消耗蜕皮免疫本次伤害并恢复20%生命（每场战斗1次）</t>
+          <t>启动急速再生程序，立即恢复自身25%最大生命值，并在接下来的2回合内每回合恢复5%</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>survive_heal</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
+          <t>healPercent</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>0.25</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>T_AN06</t>
+          <t>T_animal_06</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1290,42 +1313,40 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>虫群意志</t>
+          <t>信息素干扰</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Swarm Mind</t>
+          <t>Pheromone Jam</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>passive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>生命值越低，攻击力和速度越高，最高提升30%</t>
+          <t>释放变异信息素干扰敌方神经信号，降低敌方全体命中率和闪避率各15%，持续2回合</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>low_hp_boost</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
+          <t>debuff</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>0.15</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>T_ME01</t>
+          <t>T_mech_01</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1335,7 +1356,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>warchariot</t>
+          <t>warVehicle</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1345,17 +1366,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>War Chariot</t>
+          <t>War Vehicle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>冲撞碾压</t>
+          <t>装甲冲锋</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crush Charge</t>
+          <t>Armor Charge</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1365,27 +1386,25 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>驾驶战车冲撞，对前排敌人造成150%伤害并击退</t>
+          <t>启动履带全速冲锋，对敌方前排造成攻击力45%的伤害并击退1格，附带1回合眩晕</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>front_damage_knockback</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>1.5</t>
-        </is>
+          <t>singleDamage</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>0.45</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T_ME02</t>
+          <t>T_mech_02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1410,42 +1429,40 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>侦查扫描</t>
+          <t>蜂群扫描</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Scan Protocol</t>
+          <t>Swarm Scan</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>passive</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>扫描全体敌人，降低其闪避率25%和防御力15%，持续2回合</t>
+          <t>微型无人机群持续扫描战场，己方全体暴击率提升8%，且攻击时有15%概率附加额外一次攻击力20%的伤害</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>debuff_aoe</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.25,0.15,2</t>
-        </is>
+          <t>critBoost</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>0.08</v>
       </c>
       <c r="L17" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T_ME03</t>
+          <t>T_mech_03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1470,12 +1487,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>纳米修复</t>
+          <t>纳米注射</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nano Repair</t>
+          <t>Nano Injection</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1485,18 +1502,16 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>释放纳米机器人，治疗单体友军50%最大生命值并清除1个debuff</t>
+          <t>对己方生命值最低的单位发射纳米修复针，立即恢复其最大生命值的20%，并清除1个负面状态</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>heal_cleanse</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+          <t>healPercent</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>0.2</v>
       </c>
       <c r="L18" t="n">
         <v>3</v>
@@ -1505,7 +1520,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T_ME04</t>
+          <t>T_mech_04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1530,7 +1545,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>过载运转</t>
+          <t>超载运转</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1540,32 +1555,30 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>passive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>生命值低于50%时，攻击力提升25%，但每回合损失3%最大生命值</t>
+          <t>引擎超载运转，自身攻击力提升25%但防御力降低15%，持续3回合，结束后进入1回合冷却状态</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>low_hp_atk_self_damage</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0.25,0.03</t>
-        </is>
+          <t>selfBuff</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>0.25</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T_ME05</t>
+          <t>T_mech_05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1590,12 +1603,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>战术计算</t>
+          <t>战术锁定</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tactical Calc</t>
+          <t>Tactical Lock</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1605,18 +1618,16 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>每次攻击后，暴击率永久提升3%，最高叠加5层</t>
+          <t>军用级火控系统锁定目标，对生命值低于30%的敌人伤害提升20%，且攻击必定命中</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>crit_stack</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0.03,5</t>
-        </is>
+          <t>executeBoost</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>0.2</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1625,7 +1636,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T_ME06</t>
+          <t>T_mech_06</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1650,12 +1661,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>紧急改装</t>
+          <t>应急协议</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Emergency Mod</t>
+          <t>Emergency Protocol</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1665,18 +1676,16 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>每3回合自动修复自身10%最大生命值的护盾</t>
+          <t>民用机体的应急生存程序，当生命值首次降至20%以下时，自动触发护盾吸收相当于最大生命值30%的伤害</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>periodic_shield</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0.1,3</t>
-        </is>
+          <t>emergencyShield</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>0.3</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -1685,7 +1694,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T_EN01</t>
+          <t>T_energy_01</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1695,7 +1704,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>fire</t>
+          <t>flame</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1705,17 +1714,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Flame</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>烈焰爆发</t>
+          <t>燃烬领域</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Flame Burst</t>
+          <t>Burning Domain</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1725,27 +1734,25 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>引爆火焰能量，对全体敌人造成120%伤害并附加灼烧（每回合10%攻击力伤害，持续3回合）</t>
+          <t>在目标区域点燃持续3回合的烈焰地带，处于其中的敌方每回合受到攻击力18%的灼烧伤害</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>aoe_damage_burn</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>1.2,0.1,3</t>
-        </is>
+          <t>dotDamage</t>
+        </is>
+      </c>
+      <c r="K22" t="n">
+        <v>0.18</v>
       </c>
       <c r="L22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>T_EN02</t>
+          <t>T_energy_02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1755,7 +1762,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ice</t>
+          <t>frost</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1765,7 +1772,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ice</t>
+          <t>Frost</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1785,18 +1792,16 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>释放极寒之力，冻结单体敌人2回合，并造成100%伤害</t>
+          <t>释放极低温能量冻结目标，造成攻击力35%的伤害并冰封2回合，目标无法行动且防御降低20%</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>single_damage_freeze</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>1.0,2</t>
-        </is>
+          <t>singleDamage</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>0.35</v>
       </c>
       <c r="L23" t="n">
         <v>4</v>
@@ -1805,7 +1810,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>T_EN03</t>
+          <t>T_energy_03</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1830,12 +1835,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>连锁闪电</t>
+          <t>链式放电</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Chain Lightning</t>
+          <t>Chain Discharge</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1845,18 +1850,16 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>释放闪电链，弹射4次，每次造成70%伤害</t>
+          <t>释放高压电弧在敌方之间跳跃，对最多3个目标各造成攻击力30%的伤害，有25%概率附加1回合麻痹</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>chain_damage</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>0.7,4</t>
-        </is>
+          <t>chainDamage</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>0.3</v>
       </c>
       <c r="L24" t="n">
         <v>3</v>
@@ -1865,7 +1868,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>T_EN04</t>
+          <t>T_energy_04</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1875,7 +1878,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>light_energy</t>
+          <t>lightEnergy</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1890,12 +1893,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>圣光庇护</t>
+          <t>辐射净化</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Holy Sanctuary</t>
+          <t>Radiant Purge</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1905,18 +1908,16 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>为全体友军施加圣光护盾，吸收相当于施法者攻击力50%的伤害，持续2回合</t>
+          <t>释放高能光束净化目标区域，对敌方全体造成攻击力22%的伤害，并驱散所有增益状态</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>team_shield</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>0.5,2</t>
-        </is>
+          <t>aoeDamage</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>0.22</v>
       </c>
       <c r="L25" t="n">
         <v>5</v>
@@ -1925,7 +1926,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>T_EN05</t>
+          <t>T_energy_05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1935,7 +1936,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>dark_energy</t>
+          <t>darkEnergy</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1950,12 +1951,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>暗影吞噬</t>
+          <t>暗物质侵蚀</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Shadow Devour</t>
+          <t>Dark Matter Erosion</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1965,18 +1966,16 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>用暗能量吞噬单体敌人，造成160%伤害并吸取20%生命值</t>
+          <t>凝聚暗物质侵蚀目标护甲，造成攻击力40%的伤害并降低目标防御25%，持续2回合</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>single_damage_drain</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>1.6,0.2</t>
-        </is>
+          <t>singleDamage</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>0.4</v>
       </c>
       <c r="L26" t="n">
         <v>3</v>
@@ -1985,7 +1984,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>T_EN06</t>
+          <t>T_energy_06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2010,12 +2009,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>辐射场</t>
+          <t>辐射适应</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Radiation Field</t>
+          <t>Radiation Adaptation</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2025,18 +2024,16 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>回合开始时，对周围敌人造成攻击力15%的辐射伤害，并降低其攻击力5%（可叠加3层）</t>
+          <t>辐射基因完全觉醒，免疫所有辐射类负面效果，且每回合自动恢复2%最大生命值，在辐射环境中恢复量翻倍</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>aura_damage_debuff</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0.15,0.05,3</t>
-        </is>
+          <t>healPercent</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>0.02</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -2045,7 +2042,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>T_HY01</t>
+          <t>T_hybrid_01</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2055,7 +2052,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>bio_mech</t>
+          <t>bioPlant</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2065,47 +2062,45 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bio-Mech</t>
+          <t>Bio-Plant</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>共生强化</t>
+          <t>共生光合</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Symbiotic Boost</t>
+          <t>Symbiotic Photosynthesis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>passive</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>激活共生系统，自身攻击力+30%、生命回复+10%，持续3回合</t>
+          <t>动物与植物基因达成完美共生，每回合自动恢复4%最大生命值，且攻击时有10%概率恢复等量生命值</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>self_buff</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>0.3,0.1,3</t>
-        </is>
+          <t>healPercent</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>0.04</v>
       </c>
       <c r="L28" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>T_HY02</t>
+          <t>T_hybrid_02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2115,7 +2110,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>mech_plant</t>
+          <t>mechPlant</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2130,42 +2125,40 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>光合引擎</t>
+          <t>纳米根系</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Solar Engine</t>
+          <t>Nano Root System</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>passive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>每回合自动恢复8%最大生命值，攻击力随战斗回合数提升（每回合+2%，最高10%）</t>
+          <t>将纳米根系植入地面，吸取地脉能量为全队恢复最大生命值的12%，并提升全队防御10%，持续2回合</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>regen_atk_over_time</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>0.08,0.02,0.1</t>
-        </is>
+          <t>teamHeal</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>0.12</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>T_HY03</t>
+          <t>T_hybrid_03</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2175,7 +2168,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>mech_animal</t>
+          <t>mechAnimal</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2190,42 +2183,40 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>野兽本能</t>
+          <t>合金利爪</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Beast Instinct</t>
+          <t>Alloy Claw</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>passive</t>
+          <t>active</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>暴击时额外造成50%伤害，并使下次攻击必定暴击</t>
+          <t>机械与动物基因融合产生的合金利爪撕裂目标，造成攻击力65%的伤害，无视目标30%防御</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>crit_cascade</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>0.5</t>
-        </is>
+          <t>singleDamage</t>
+        </is>
+      </c>
+      <c r="K30" t="n">
+        <v>0.65</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>T_HY04</t>
+          <t>T_hybrid_04</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2235,7 +2226,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>energy_mix</t>
+          <t>energyMix</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2250,12 +2241,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>元素共鸣</t>
+          <t>双元爆发</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Elemental Resonance</t>
+          <t>Dual Burst</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2265,27 +2256,25 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>引发元素共鸣，随机释放一种元素AOE攻击（130%伤害），并附加对应元素效果</t>
+          <t>同时释放两种能量形成毁灭性冲击波，对敌方全体造成攻击力35%的伤害，随机附加灼烧或冰冻效果</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>random_element_aoe</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>1.3</t>
-        </is>
+          <t>aoeDamage</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>0.35</v>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>T_HY05</t>
+          <t>T_hybrid_05</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2295,7 +2284,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>triple_mix</t>
+          <t>triMix</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2305,47 +2294,45 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Triple Mix</t>
+          <t>Tri-Mix</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>三系融合</t>
+          <t>三重共鸣</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Triple Fusion</t>
+          <t>Triple Resonance</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>passive</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>融合三种力量，对全体敌人造成150%伤害，同时治疗全体友军20%最大生命值</t>
+          <t>三系基因产生共鸣效应，所有属性永久提升8%，且每次使用技能后有20%概率不消耗行动点</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>aoe_damage_heal</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>1.5,0.2</t>
-        </is>
+          <t>allStatBoost</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>0.08</v>
       </c>
       <c r="L32" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>T_HY06</t>
+          <t>T_hybrid_06</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2370,36 +2357,34 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>混沌之力</t>
+          <t>混沌突变</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaos Power</t>
+          <t>Chaos Mutation</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>active</t>
+          <t>passive</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>释放混沌能量，随机效果：200%单体伤害/全体30%治疗/全体buff攻击+20%</t>
+          <t>混沌基因每回合随机变异，每回合开始时随机获得一项增益：攻击+15%、防御+15%、速度+15%或回复10%生命值</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>random_effect</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>2.0,0.3,0.2</t>
-        </is>
+          <t>randomBuff</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>0.15</v>
       </c>
       <c r="L33" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
